--- a/modules/log/[Админ] Ербол.xlsx
+++ b/modules/log/[Админ] Ербол.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -487,9 +487,53 @@
         <v>52</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>[Админ] Ербол</v>
+      </c>
+      <c r="B3" t="str">
+        <v>44</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Кожакова</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Шахабиддина 71</v>
+      </c>
+      <c r="E3" t="str">
+        <v>7</v>
+      </c>
+      <c r="F3" t="str">
+        <v>505</v>
+      </c>
+      <c r="G3" t="str">
+        <v>1414</v>
+      </c>
+      <c r="H3" t="str">
+        <v>1420</v>
+      </c>
+      <c r="I3" t="str">
+        <v>6</v>
+      </c>
+      <c r="J3" t="str">
+        <v>2024</v>
+      </c>
+      <c r="K3" t="str">
+        <v>6</v>
+      </c>
+      <c r="L3" t="str">
+        <v>5</v>
+      </c>
+      <c r="M3" t="str">
+        <v>12</v>
+      </c>
+      <c r="N3" t="str">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N3"/>
   </ignoredErrors>
 </worksheet>
 </file>